--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
   <si>
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 23 Agu 2026, 12.04 | Dicetak: 23 Agu 2026, 12.52</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 23 Agu 2026, 18.04 | Dicetak: 23 Agu 2026, 20.21</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>7,59</t>
+    <t>7,56</t>
   </si>
   <si>
     <t>1801</t>
@@ -82,7 +82,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>3,16</t>
+    <t>3,22</t>
   </si>
   <si>
     <t>1804</t>
@@ -91,7 +91,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>2,08</t>
+    <t>2,12</t>
   </si>
   <si>
     <t>1805</t>
@@ -100,7 +100,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>2,59</t>
+    <t>2,56</t>
   </si>
   <si>
     <t>1806</t>
@@ -127,7 +127,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>15,74</t>
+    <t>15,77</t>
   </si>
   <si>
     <t>1809</t>
@@ -136,7 +136,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>20,27</t>
+    <t>20,23</t>
   </si>
   <si>
     <t>1810</t>
@@ -154,7 +154,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>25,25</t>
+    <t>24,36</t>
   </si>
   <si>
     <t>1812</t>
@@ -172,7 +172,7 @@
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>28,06</t>
+    <t>27,41</t>
   </si>
   <si>
     <t>1871</t>
@@ -181,13 +181,16 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>0,52</t>
+    <t>0,58</t>
   </si>
   <si>
     <t>1872</t>
   </si>
   <si>
     <t>METRO</t>
+  </si>
+  <si>
+    <t>3,27</t>
   </si>
   <si>
     <t/>
@@ -756,7 +759,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>3748</v>
+        <v>3734</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -807,7 +810,7 @@
         <v>5816</v>
       </c>
       <c r="D9" s="9">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>23</v>
@@ -824,7 +827,7 @@
         <v>6824</v>
       </c>
       <c r="D10" s="9">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
@@ -841,7 +844,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -892,7 +895,7 @@
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>38</v>
@@ -909,7 +912,7 @@
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>41</v>
@@ -943,7 +946,7 @@
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>47</v>
@@ -977,7 +980,7 @@
         <v>613</v>
       </c>
       <c r="D19" s="9">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>53</v>
@@ -994,7 +997,7 @@
         <v>3432</v>
       </c>
       <c r="D20" s="9">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>56</v>
@@ -1011,24 +1014,24 @@
         <v>855</v>
       </c>
       <c r="D21" s="9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C22" s="12">
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>3748</v>
+        <v>3734</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>

--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 23 Agu 2026, 18.04 | Dicetak: 23 Agu 2026, 20.21</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 24 Agu 2026, 06.04 | Dicetak: 24 Agu 2026, 07.46</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>7,56</t>
+    <t>7,65</t>
   </si>
   <si>
     <t>1801</t>
@@ -73,7 +73,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>0,76</t>
+    <t>0,94</t>
   </si>
   <si>
     <t>1803</t>
@@ -82,7 +82,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>3,22</t>
+    <t>3,35</t>
   </si>
   <si>
     <t>1804</t>
@@ -91,7 +91,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>2,12</t>
+    <t>2,1</t>
   </si>
   <si>
     <t>1805</t>
@@ -100,7 +100,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>2,56</t>
+    <t>2,58</t>
   </si>
   <si>
     <t>1806</t>
@@ -109,7 +109,7 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>15,39</t>
+    <t>16,06</t>
   </si>
   <si>
     <t>1807</t>
@@ -118,7 +118,7 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>1,17</t>
+    <t>1,2</t>
   </si>
   <si>
     <t>1808</t>
@@ -127,7 +127,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>15,77</t>
+    <t>16,05</t>
   </si>
   <si>
     <t>1809</t>
@@ -136,7 +136,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>20,23</t>
+    <t>20,34</t>
   </si>
   <si>
     <t>1810</t>
@@ -145,7 +145,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>11,46</t>
+    <t>11,9</t>
   </si>
   <si>
     <t>1811</t>
@@ -154,7 +154,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>24,36</t>
+    <t>23,97</t>
   </si>
   <si>
     <t>1812</t>
@@ -163,7 +163,7 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>19,92</t>
+    <t>19,68</t>
   </si>
   <si>
     <t>1813</t>
@@ -172,7 +172,7 @@
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>27,41</t>
+    <t>26,43</t>
   </si>
   <si>
     <t>1871</t>
@@ -181,7 +181,7 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>0,58</t>
+    <t>0,67</t>
   </si>
   <si>
     <t>1872</t>
@@ -759,7 +759,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>3734</v>
+        <v>3780</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -793,7 +793,7 @@
         <v>2756</v>
       </c>
       <c r="D8" s="9">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
@@ -810,7 +810,7 @@
         <v>5816</v>
       </c>
       <c r="D9" s="9">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>23</v>
@@ -827,7 +827,7 @@
         <v>6824</v>
       </c>
       <c r="D10" s="9">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -861,7 +861,7 @@
         <v>4022</v>
       </c>
       <c r="D12" s="9">
-        <v>619</v>
+        <v>646</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -878,7 +878,7 @@
         <v>2905</v>
       </c>
       <c r="D13" s="9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>35</v>
@@ -895,7 +895,7 @@
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>38</v>
@@ -912,7 +912,7 @@
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>41</v>
@@ -929,7 +929,7 @@
         <v>1605</v>
       </c>
       <c r="D16" s="9">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>44</v>
@@ -946,7 +946,7 @@
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>47</v>
@@ -963,7 +963,7 @@
         <v>2485</v>
       </c>
       <c r="D18" s="9">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>50</v>
@@ -980,7 +980,7 @@
         <v>613</v>
       </c>
       <c r="D19" s="9">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>53</v>
@@ -997,7 +997,7 @@
         <v>3432</v>
       </c>
       <c r="D20" s="9">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>56</v>
@@ -1031,7 +1031,7 @@
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>3734</v>
+        <v>3780</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>

--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 24 Agu 2026, 06.04 | Dicetak: 24 Agu 2026, 07.46</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 24 Agu 2026, 18.04 | Dicetak: 24 Agu 2026, 21.08</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>7,65</t>
+    <t>7,8</t>
   </si>
   <si>
     <t>1801</t>
@@ -82,7 +82,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>3,35</t>
+    <t>3,51</t>
   </si>
   <si>
     <t>1804</t>
@@ -91,7 +91,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>2,1</t>
+    <t>2,15</t>
   </si>
   <si>
     <t>1805</t>
@@ -100,7 +100,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>2,58</t>
+    <t>2,6</t>
   </si>
   <si>
     <t>1806</t>
@@ -109,7 +109,7 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>16,06</t>
+    <t>16,01</t>
   </si>
   <si>
     <t>1807</t>
@@ -127,7 +127,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>16,05</t>
+    <t>16,03</t>
   </si>
   <si>
     <t>1809</t>
@@ -136,7 +136,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>20,34</t>
+    <t>21,76</t>
   </si>
   <si>
     <t>1810</t>
@@ -145,7 +145,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>11,9</t>
+    <t>12,15</t>
   </si>
   <si>
     <t>1811</t>
@@ -154,7 +154,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>23,97</t>
+    <t>23,81</t>
   </si>
   <si>
     <t>1812</t>
@@ -163,7 +163,7 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>19,68</t>
+    <t>20,85</t>
   </si>
   <si>
     <t>1813</t>
@@ -172,7 +172,7 @@
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>26,43</t>
+    <t>24,63</t>
   </si>
   <si>
     <t>1871</t>
@@ -181,7 +181,7 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>0,67</t>
+    <t>0,73</t>
   </si>
   <si>
     <t>1872</t>
@@ -190,7 +190,7 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>3,27</t>
+    <t>3,04</t>
   </si>
   <si>
     <t/>
@@ -759,7 +759,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>3780</v>
+        <v>3850</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -810,7 +810,7 @@
         <v>5816</v>
       </c>
       <c r="D9" s="9">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>23</v>
@@ -827,7 +827,7 @@
         <v>6824</v>
       </c>
       <c r="D10" s="9">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -861,7 +861,7 @@
         <v>4022</v>
       </c>
       <c r="D12" s="9">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -895,7 +895,7 @@
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>38</v>
@@ -912,7 +912,7 @@
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>560</v>
+        <v>599</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>41</v>
@@ -929,7 +929,7 @@
         <v>1605</v>
       </c>
       <c r="D16" s="9">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>44</v>
@@ -946,7 +946,7 @@
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>47</v>
@@ -963,7 +963,7 @@
         <v>2485</v>
       </c>
       <c r="D18" s="9">
-        <v>489</v>
+        <v>518</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>50</v>
@@ -980,7 +980,7 @@
         <v>613</v>
       </c>
       <c r="D19" s="9">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>53</v>
@@ -997,7 +997,7 @@
         <v>3432</v>
       </c>
       <c r="D20" s="9">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>56</v>
@@ -1014,7 +1014,7 @@
         <v>855</v>
       </c>
       <c r="D21" s="9">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>59</v>
@@ -1031,7 +1031,7 @@
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>3780</v>
+        <v>3850</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>

--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 24 Agu 2026, 18.04 | Dicetak: 24 Agu 2026, 21.08</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 25 Agu 2026, 06.04 | Dicetak: 25 Agu 2026, 07.58</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>7,8</t>
+    <t>8,91</t>
   </si>
   <si>
     <t>1801</t>
@@ -82,7 +82,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>3,51</t>
+    <t>3,52</t>
   </si>
   <si>
     <t>1804</t>
@@ -91,7 +91,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>2,15</t>
+    <t>2,24</t>
   </si>
   <si>
     <t>1805</t>
@@ -100,7 +100,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>2,6</t>
+    <t>3</t>
   </si>
   <si>
     <t>1806</t>
@@ -109,7 +109,7 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>16,01</t>
+    <t>17,23</t>
   </si>
   <si>
     <t>1807</t>
@@ -127,7 +127,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>16,03</t>
+    <t>16,13</t>
   </si>
   <si>
     <t>1809</t>
@@ -136,7 +136,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>21,76</t>
+    <t>21,65</t>
   </si>
   <si>
     <t>1810</t>
@@ -145,7 +145,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>12,15</t>
+    <t>12,59</t>
   </si>
   <si>
     <t>1811</t>
@@ -154,7 +154,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>23,81</t>
+    <t>23,7</t>
   </si>
   <si>
     <t>1812</t>
@@ -163,7 +163,7 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>20,85</t>
+    <t>39,24</t>
   </si>
   <si>
     <t>1813</t>
@@ -172,7 +172,7 @@
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>24,63</t>
+    <t>23,98</t>
   </si>
   <si>
     <t>1871</t>
@@ -759,7 +759,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>3850</v>
+        <v>4399</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -810,7 +810,7 @@
         <v>5816</v>
       </c>
       <c r="D9" s="9">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>23</v>
@@ -827,7 +827,7 @@
         <v>6824</v>
       </c>
       <c r="D10" s="9">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>224</v>
+        <v>258</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -861,7 +861,7 @@
         <v>4022</v>
       </c>
       <c r="D12" s="9">
-        <v>644</v>
+        <v>693</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -895,7 +895,7 @@
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>38</v>
@@ -912,7 +912,7 @@
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>41</v>
@@ -929,7 +929,7 @@
         <v>1605</v>
       </c>
       <c r="D16" s="9">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>44</v>
@@ -946,7 +946,7 @@
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>47</v>
@@ -963,7 +963,7 @@
         <v>2485</v>
       </c>
       <c r="D18" s="9">
-        <v>518</v>
+        <v>975</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>50</v>
@@ -980,7 +980,7 @@
         <v>613</v>
       </c>
       <c r="D19" s="9">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>53</v>
@@ -1031,7 +1031,7 @@
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>3850</v>
+        <v>4399</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>

--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 27 Agu 2026, 12.04 | Dicetak: 27 Agu 2026, 12.58</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 28 Agu 2026, 06.04 | Dicetak: 28 Agu 2026, 09.33</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>10,55</t>
+    <t>12,86</t>
   </si>
   <si>
     <t>1801</t>
@@ -64,7 +64,7 @@
     <t>LAMPUNG BARAT</t>
   </si>
   <si>
-    <t>0,79</t>
+    <t>1,19</t>
   </si>
   <si>
     <t>1802</t>
@@ -73,7 +73,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>1,05</t>
+    <t>1,2</t>
   </si>
   <si>
     <t>1803</t>
@@ -100,7 +100,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>3,17</t>
+    <t>4,76</t>
   </si>
   <si>
     <t>1806</t>
@@ -109,7 +109,7 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>17,43</t>
+    <t>19,99</t>
   </si>
   <si>
     <t>1807</t>
@@ -118,7 +118,7 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>1,38</t>
+    <t>1,55</t>
   </si>
   <si>
     <t>1808</t>
@@ -127,7 +127,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>17,9</t>
+    <t>19,56</t>
   </si>
   <si>
     <t>1809</t>
@@ -136,7 +136,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>22,12</t>
+    <t>22,05</t>
   </si>
   <si>
     <t>1810</t>
@@ -145,7 +145,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>15,45</t>
+    <t>17,38</t>
   </si>
   <si>
     <t>1811</t>
@@ -154,7 +154,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>25,97</t>
+    <t>27,58</t>
   </si>
   <si>
     <t>1812</t>
@@ -163,7 +163,7 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>61,93</t>
+    <t>92,56</t>
   </si>
   <si>
     <t>1813</t>
@@ -172,7 +172,7 @@
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>20,88</t>
+    <t>21,21</t>
   </si>
   <si>
     <t>1871</t>
@@ -190,7 +190,7 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>3,51</t>
+    <t>3,74</t>
   </si>
   <si>
     <t/>
@@ -759,7 +759,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>5209</v>
+        <v>6350</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -776,7 +776,7 @@
         <v>1011</v>
       </c>
       <c r="D7" s="9">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>17</v>
@@ -793,7 +793,7 @@
         <v>2756</v>
       </c>
       <c r="D8" s="9">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
@@ -844,7 +844,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>273</v>
+        <v>410</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -861,7 +861,7 @@
         <v>4022</v>
       </c>
       <c r="D12" s="9">
-        <v>701</v>
+        <v>804</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -878,7 +878,7 @@
         <v>2905</v>
       </c>
       <c r="D13" s="9">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>35</v>
@@ -895,7 +895,7 @@
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>698</v>
+        <v>763</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>38</v>
@@ -912,7 +912,7 @@
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>41</v>
@@ -929,7 +929,7 @@
         <v>1605</v>
       </c>
       <c r="D16" s="9">
-        <v>248</v>
+        <v>279</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>44</v>
@@ -946,7 +946,7 @@
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>468</v>
+        <v>497</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>47</v>
@@ -963,7 +963,7 @@
         <v>2485</v>
       </c>
       <c r="D18" s="9">
-        <v>1539</v>
+        <v>2300</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>50</v>
@@ -980,7 +980,7 @@
         <v>613</v>
       </c>
       <c r="D19" s="9">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>53</v>
@@ -1014,7 +1014,7 @@
         <v>855</v>
       </c>
       <c r="D21" s="9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>59</v>
@@ -1031,7 +1031,7 @@
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>5209</v>
+        <v>6350</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>

--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 28 Agu 2026, 06.04 | Dicetak: 28 Agu 2026, 09.33</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 29 Agu 2026, 12.04 | Dicetak: 29 Agu 2026, 16.17</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>12,86</t>
+    <t>15,96</t>
   </si>
   <si>
     <t>1801</t>
@@ -64,7 +64,7 @@
     <t>LAMPUNG BARAT</t>
   </si>
   <si>
-    <t>1,19</t>
+    <t>6,13</t>
   </si>
   <si>
     <t>1802</t>
@@ -73,7 +73,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>1,2</t>
+    <t>7,58</t>
   </si>
   <si>
     <t>1803</t>
@@ -82,7 +82,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>4,66</t>
+    <t>5,81</t>
   </si>
   <si>
     <t>1804</t>
@@ -91,7 +91,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>2,1</t>
+    <t>2,08</t>
   </si>
   <si>
     <t>1805</t>
@@ -100,7 +100,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>4,76</t>
+    <t>8,71</t>
   </si>
   <si>
     <t>1806</t>
@@ -109,7 +109,7 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>19,99</t>
+    <t>33,79</t>
   </si>
   <si>
     <t>1807</t>
@@ -118,7 +118,7 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>1,55</t>
+    <t>2,55</t>
   </si>
   <si>
     <t>1808</t>
@@ -127,7 +127,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>19,56</t>
+    <t>22</t>
   </si>
   <si>
     <t>1809</t>
@@ -136,7 +136,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>22,05</t>
+    <t>22,16</t>
   </si>
   <si>
     <t>1810</t>
@@ -145,7 +145,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>17,38</t>
+    <t>22,8</t>
   </si>
   <si>
     <t>1811</t>
@@ -154,7 +154,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>27,58</t>
+    <t>27,3</t>
   </si>
   <si>
     <t>1812</t>
@@ -163,7 +163,7 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>92,56</t>
+    <t>98,51</t>
   </si>
   <si>
     <t>1813</t>
@@ -172,7 +172,7 @@
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>21,21</t>
+    <t>19,58</t>
   </si>
   <si>
     <t>1871</t>
@@ -181,7 +181,7 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>0,7</t>
+    <t>0,76</t>
   </si>
   <si>
     <t>1872</t>
@@ -190,7 +190,7 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>3,74</t>
+    <t>3,51</t>
   </si>
   <si>
     <t/>
@@ -759,7 +759,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>6350</v>
+        <v>7884</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -776,7 +776,7 @@
         <v>1011</v>
       </c>
       <c r="D7" s="9">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>17</v>
@@ -793,7 +793,7 @@
         <v>2756</v>
       </c>
       <c r="D8" s="9">
-        <v>33</v>
+        <v>209</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
@@ -810,7 +810,7 @@
         <v>5816</v>
       </c>
       <c r="D9" s="9">
-        <v>271</v>
+        <v>338</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>23</v>
@@ -827,7 +827,7 @@
         <v>6824</v>
       </c>
       <c r="D10" s="9">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>410</v>
+        <v>750</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -861,7 +861,7 @@
         <v>4022</v>
       </c>
       <c r="D12" s="9">
-        <v>804</v>
+        <v>1359</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -878,7 +878,7 @@
         <v>2905</v>
       </c>
       <c r="D13" s="9">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>35</v>
@@ -895,7 +895,7 @@
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>763</v>
+        <v>858</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>38</v>
@@ -912,7 +912,7 @@
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>41</v>
@@ -929,7 +929,7 @@
         <v>1605</v>
       </c>
       <c r="D16" s="9">
-        <v>279</v>
+        <v>366</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>44</v>
@@ -946,7 +946,7 @@
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>47</v>
@@ -963,7 +963,7 @@
         <v>2485</v>
       </c>
       <c r="D18" s="9">
-        <v>2300</v>
+        <v>2448</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>50</v>
@@ -980,7 +980,7 @@
         <v>613</v>
       </c>
       <c r="D19" s="9">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>53</v>
@@ -997,7 +997,7 @@
         <v>3432</v>
       </c>
       <c r="D20" s="9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>56</v>
@@ -1014,7 +1014,7 @@
         <v>855</v>
       </c>
       <c r="D21" s="9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>59</v>
@@ -1031,7 +1031,7 @@
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>6350</v>
+        <v>7884</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>

--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 29 Agu 2026, 12.04 | Dicetak: 29 Agu 2026, 16.17</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 31 Agu 2026, 06.04 | Dicetak: 31 Agu 2026, 08.56</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>15,96</t>
+    <t>22,62</t>
   </si>
   <si>
     <t>1801</t>
@@ -64,70 +64,70 @@
     <t>LAMPUNG BARAT</t>
   </si>
   <si>
+    <t>13,25</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>10,78</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>6,29</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>7,3</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>17,75</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>50,57</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
     <t>6,13</t>
   </si>
   <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>7,58</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>5,81</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>2,08</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>8,71</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>33,79</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>2,55</t>
-  </si>
-  <si>
     <t>1808</t>
   </si>
   <si>
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>22</t>
+    <t>24,56</t>
   </si>
   <si>
     <t>1809</t>
@@ -136,7 +136,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>22,16</t>
+    <t>36,91</t>
   </si>
   <si>
     <t>1810</t>
@@ -145,7 +145,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>22,8</t>
+    <t>24,86</t>
   </si>
   <si>
     <t>1811</t>
@@ -154,7 +154,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>27,3</t>
+    <t>64,71</t>
   </si>
   <si>
     <t>1812</t>
@@ -163,7 +163,7 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>98,51</t>
+    <t>94,16</t>
   </si>
   <si>
     <t>1813</t>
@@ -172,7 +172,7 @@
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>19,58</t>
+    <t>18,92</t>
   </si>
   <si>
     <t>1871</t>
@@ -181,7 +181,7 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>0,76</t>
+    <t>1,52</t>
   </si>
   <si>
     <t>1872</t>
@@ -190,7 +190,7 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>3,51</t>
+    <t>10,53</t>
   </si>
   <si>
     <t/>
@@ -759,7 +759,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>7884</v>
+        <v>11172</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -776,7 +776,7 @@
         <v>1011</v>
       </c>
       <c r="D7" s="9">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>17</v>
@@ -793,7 +793,7 @@
         <v>2756</v>
       </c>
       <c r="D8" s="9">
-        <v>209</v>
+        <v>297</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
@@ -810,7 +810,7 @@
         <v>5816</v>
       </c>
       <c r="D9" s="9">
-        <v>338</v>
+        <v>366</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>23</v>
@@ -827,7 +827,7 @@
         <v>6824</v>
       </c>
       <c r="D10" s="9">
-        <v>142</v>
+        <v>498</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>750</v>
+        <v>1528</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -861,7 +861,7 @@
         <v>4022</v>
       </c>
       <c r="D12" s="9">
-        <v>1359</v>
+        <v>2034</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -878,7 +878,7 @@
         <v>2905</v>
       </c>
       <c r="D13" s="9">
-        <v>74</v>
+        <v>178</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>35</v>
@@ -895,7 +895,7 @@
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>858</v>
+        <v>958</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>38</v>
@@ -912,7 +912,7 @@
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>610</v>
+        <v>1016</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>41</v>
@@ -929,7 +929,7 @@
         <v>1605</v>
       </c>
       <c r="D16" s="9">
-        <v>366</v>
+        <v>399</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>44</v>
@@ -946,7 +946,7 @@
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>492</v>
+        <v>1166</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>47</v>
@@ -963,7 +963,7 @@
         <v>2485</v>
       </c>
       <c r="D18" s="9">
-        <v>2448</v>
+        <v>2340</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>50</v>
@@ -980,7 +980,7 @@
         <v>613</v>
       </c>
       <c r="D19" s="9">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>53</v>
@@ -997,7 +997,7 @@
         <v>3432</v>
       </c>
       <c r="D20" s="9">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>56</v>
@@ -1014,7 +1014,7 @@
         <v>855</v>
       </c>
       <c r="D21" s="9">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>59</v>
@@ -1031,7 +1031,7 @@
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>7884</v>
+        <v>11172</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>

--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 31 Agu 2026, 06.04 | Dicetak: 31 Agu 2026, 08.56</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 1 Sep 2026, 12.04 | Dicetak: 1 Sep 2026, 13.01</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>22,62</t>
+    <t>28,72</t>
   </si>
   <si>
     <t>1801</t>
@@ -64,7 +64,7 @@
     <t>LAMPUNG BARAT</t>
   </si>
   <si>
-    <t>13,25</t>
+    <t>12,66</t>
   </si>
   <si>
     <t>1802</t>
@@ -73,7 +73,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>10,78</t>
+    <t>12,37</t>
   </si>
   <si>
     <t>1803</t>
@@ -82,7 +82,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>6,29</t>
+    <t>6,67</t>
   </si>
   <si>
     <t>1804</t>
@@ -91,7 +91,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>7,3</t>
+    <t>9,5</t>
   </si>
   <si>
     <t>1805</t>
@@ -100,7 +100,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>17,75</t>
+    <t>21,22</t>
   </si>
   <si>
     <t>1806</t>
@@ -109,7 +109,7 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>50,57</t>
+    <t>76,43</t>
   </si>
   <si>
     <t>1807</t>
@@ -118,7 +118,7 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>6,13</t>
+    <t>11,57</t>
   </si>
   <si>
     <t>1808</t>
@@ -127,7 +127,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>24,56</t>
+    <t>28,31</t>
   </si>
   <si>
     <t>1809</t>
@@ -136,7 +136,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>36,91</t>
+    <t>56,48</t>
   </si>
   <si>
     <t>1810</t>
@@ -145,7 +145,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>24,86</t>
+    <t>39,94</t>
   </si>
   <si>
     <t>1811</t>
@@ -154,7 +154,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>64,71</t>
+    <t>79,02</t>
   </si>
   <si>
     <t>1812</t>
@@ -163,7 +163,7 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>94,16</t>
+    <t>94,73</t>
   </si>
   <si>
     <t>1813</t>
@@ -172,7 +172,7 @@
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>18,92</t>
+    <t>26,26</t>
   </si>
   <si>
     <t>1871</t>
@@ -181,7 +181,7 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>1,52</t>
+    <t>2,59</t>
   </si>
   <si>
     <t>1872</t>
@@ -190,7 +190,7 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>10,53</t>
+    <t>13,45</t>
   </si>
   <si>
     <t/>
@@ -759,7 +759,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>11172</v>
+        <v>14184</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -776,7 +776,7 @@
         <v>1011</v>
       </c>
       <c r="D7" s="9">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>17</v>
@@ -793,7 +793,7 @@
         <v>2756</v>
       </c>
       <c r="D8" s="9">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
@@ -810,7 +810,7 @@
         <v>5816</v>
       </c>
       <c r="D9" s="9">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>23</v>
@@ -827,7 +827,7 @@
         <v>6824</v>
       </c>
       <c r="D10" s="9">
-        <v>498</v>
+        <v>648</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>1528</v>
+        <v>1826</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -861,7 +861,7 @@
         <v>4022</v>
       </c>
       <c r="D12" s="9">
-        <v>2034</v>
+        <v>3074</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -878,7 +878,7 @@
         <v>2905</v>
       </c>
       <c r="D13" s="9">
-        <v>178</v>
+        <v>336</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>35</v>
@@ -895,7 +895,7 @@
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>958</v>
+        <v>1104</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>38</v>
@@ -912,7 +912,7 @@
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>1016</v>
+        <v>1555</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>41</v>
@@ -929,7 +929,7 @@
         <v>1605</v>
       </c>
       <c r="D16" s="9">
-        <v>399</v>
+        <v>641</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>44</v>
@@ -946,7 +946,7 @@
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>1166</v>
+        <v>1424</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>47</v>
@@ -963,7 +963,7 @@
         <v>2485</v>
       </c>
       <c r="D18" s="9">
-        <v>2340</v>
+        <v>2354</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>50</v>
@@ -980,7 +980,7 @@
         <v>613</v>
       </c>
       <c r="D19" s="9">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>53</v>
@@ -997,7 +997,7 @@
         <v>3432</v>
       </c>
       <c r="D20" s="9">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>56</v>
@@ -1014,7 +1014,7 @@
         <v>855</v>
       </c>
       <c r="D21" s="9">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>59</v>
@@ -1031,7 +1031,7 @@
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>11172</v>
+        <v>14184</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>

--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 1 Sep 2026, 12.04 | Dicetak: 1 Sep 2026, 13.01</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 2 Sep 2026, 06.04 | Dicetak: 2 Sep 2026, 10.03</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>28,72</t>
+    <t>28,63</t>
   </si>
   <si>
     <t>1801</t>
@@ -64,7 +64,7 @@
     <t>LAMPUNG BARAT</t>
   </si>
   <si>
-    <t>12,66</t>
+    <t>13,75</t>
   </si>
   <si>
     <t>1802</t>
@@ -73,7 +73,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>12,37</t>
+    <t>12,19</t>
   </si>
   <si>
     <t>1803</t>
@@ -82,7 +82,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>6,67</t>
+    <t>7,05</t>
   </si>
   <si>
     <t>1804</t>
@@ -91,7 +91,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>9,5</t>
+    <t>11,33</t>
   </si>
   <si>
     <t>1805</t>
@@ -100,7 +100,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>21,22</t>
+    <t>19,84</t>
   </si>
   <si>
     <t>1806</t>
@@ -109,7 +109,7 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>76,43</t>
+    <t>79,29</t>
   </si>
   <si>
     <t>1807</t>
@@ -118,7 +118,7 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>11,57</t>
+    <t>12,15</t>
   </si>
   <si>
     <t>1808</t>
@@ -127,7 +127,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>28,31</t>
+    <t>28,18</t>
   </si>
   <si>
     <t>1809</t>
@@ -136,7 +136,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>56,48</t>
+    <t>56,37</t>
   </si>
   <si>
     <t>1810</t>
@@ -145,7 +145,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>39,94</t>
+    <t>40,87</t>
   </si>
   <si>
     <t>1811</t>
@@ -154,7 +154,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>79,02</t>
+    <t>65,37</t>
   </si>
   <si>
     <t>1812</t>
@@ -163,7 +163,7 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>94,73</t>
+    <t>94,69</t>
   </si>
   <si>
     <t>1813</t>
@@ -172,7 +172,7 @@
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>26,26</t>
+    <t>26,1</t>
   </si>
   <si>
     <t>1871</t>
@@ -181,7 +181,7 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>2,59</t>
+    <t>3,03</t>
   </si>
   <si>
     <t>1872</t>
@@ -190,7 +190,7 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>13,45</t>
+    <t>14,97</t>
   </si>
   <si>
     <t/>
@@ -759,7 +759,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>14184</v>
+        <v>14138</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -776,7 +776,7 @@
         <v>1011</v>
       </c>
       <c r="D7" s="9">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>17</v>
@@ -793,7 +793,7 @@
         <v>2756</v>
       </c>
       <c r="D8" s="9">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
@@ -810,7 +810,7 @@
         <v>5816</v>
       </c>
       <c r="D9" s="9">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>23</v>
@@ -827,7 +827,7 @@
         <v>6824</v>
       </c>
       <c r="D10" s="9">
-        <v>648</v>
+        <v>773</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>1826</v>
+        <v>1708</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -861,7 +861,7 @@
         <v>4022</v>
       </c>
       <c r="D12" s="9">
-        <v>3074</v>
+        <v>3189</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -878,7 +878,7 @@
         <v>2905</v>
       </c>
       <c r="D13" s="9">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>35</v>
@@ -895,7 +895,7 @@
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>38</v>
@@ -912,7 +912,7 @@
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>1555</v>
+        <v>1552</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>41</v>
@@ -929,7 +929,7 @@
         <v>1605</v>
       </c>
       <c r="D16" s="9">
-        <v>641</v>
+        <v>656</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>44</v>
@@ -946,7 +946,7 @@
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>1424</v>
+        <v>1178</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>47</v>
@@ -963,7 +963,7 @@
         <v>2485</v>
       </c>
       <c r="D18" s="9">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>50</v>
@@ -980,7 +980,7 @@
         <v>613</v>
       </c>
       <c r="D19" s="9">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>53</v>
@@ -997,7 +997,7 @@
         <v>3432</v>
       </c>
       <c r="D20" s="9">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>56</v>
@@ -1014,7 +1014,7 @@
         <v>855</v>
       </c>
       <c r="D21" s="9">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>59</v>
@@ -1031,7 +1031,7 @@
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>14184</v>
+        <v>14138</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>

--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 2 Sep 2026, 06.04 | Dicetak: 2 Sep 2026, 10.03</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 3 Sep 2026, 12.04 | Dicetak: 3 Sep 2026, 13.25</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>28,63</t>
+    <t>27,88</t>
   </si>
   <si>
     <t>1801</t>
@@ -64,7 +64,7 @@
     <t>LAMPUNG BARAT</t>
   </si>
   <si>
-    <t>13,75</t>
+    <t>91</t>
   </si>
   <si>
     <t>1802</t>
@@ -73,7 +73,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>12,19</t>
+    <t>12,99</t>
   </si>
   <si>
     <t>1803</t>
@@ -82,7 +82,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>7,05</t>
+    <t>8,29</t>
   </si>
   <si>
     <t>1804</t>
@@ -91,7 +91,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>11,33</t>
+    <t>11,87</t>
   </si>
   <si>
     <t>1805</t>
@@ -100,7 +100,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>19,84</t>
+    <t>16,07</t>
   </si>
   <si>
     <t>1806</t>
@@ -109,7 +109,7 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>79,29</t>
+    <t>79,07</t>
   </si>
   <si>
     <t>1807</t>
@@ -118,7 +118,7 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>12,15</t>
+    <t>13,43</t>
   </si>
   <si>
     <t>1808</t>
@@ -127,7 +127,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>28,18</t>
+    <t>26,62</t>
   </si>
   <si>
     <t>1809</t>
@@ -136,7 +136,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>56,37</t>
+    <t>37,6</t>
   </si>
   <si>
     <t>1810</t>
@@ -145,7 +145,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>40,87</t>
+    <t>46,73</t>
   </si>
   <si>
     <t>1811</t>
@@ -154,7 +154,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>65,37</t>
+    <t>41,34</t>
   </si>
   <si>
     <t>1812</t>
@@ -163,7 +163,7 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>94,69</t>
+    <t>89,86</t>
   </si>
   <si>
     <t>1813</t>
@@ -172,7 +172,7 @@
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>26,1</t>
+    <t>25,77</t>
   </si>
   <si>
     <t>1871</t>
@@ -181,7 +181,7 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>3,03</t>
+    <t>4,37</t>
   </si>
   <si>
     <t>1872</t>
@@ -190,7 +190,7 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>14,97</t>
+    <t>15,91</t>
   </si>
   <si>
     <t/>
@@ -759,7 +759,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>14138</v>
+        <v>13768</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -776,7 +776,7 @@
         <v>1011</v>
       </c>
       <c r="D7" s="9">
-        <v>139</v>
+        <v>920</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>17</v>
@@ -793,7 +793,7 @@
         <v>2756</v>
       </c>
       <c r="D8" s="9">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
@@ -810,7 +810,7 @@
         <v>5816</v>
       </c>
       <c r="D9" s="9">
-        <v>410</v>
+        <v>482</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>23</v>
@@ -827,7 +827,7 @@
         <v>6824</v>
       </c>
       <c r="D10" s="9">
-        <v>773</v>
+        <v>810</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>1708</v>
+        <v>1383</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -861,7 +861,7 @@
         <v>4022</v>
       </c>
       <c r="D12" s="9">
-        <v>3189</v>
+        <v>3180</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -878,7 +878,7 @@
         <v>2905</v>
       </c>
       <c r="D13" s="9">
-        <v>353</v>
+        <v>390</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>35</v>
@@ -895,7 +895,7 @@
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>1099</v>
+        <v>1038</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>38</v>
@@ -912,7 +912,7 @@
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>1552</v>
+        <v>1035</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>41</v>
@@ -929,7 +929,7 @@
         <v>1605</v>
       </c>
       <c r="D16" s="9">
-        <v>656</v>
+        <v>750</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>44</v>
@@ -946,7 +946,7 @@
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>1178</v>
+        <v>745</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>47</v>
@@ -963,7 +963,7 @@
         <v>2485</v>
       </c>
       <c r="D18" s="9">
-        <v>2353</v>
+        <v>2233</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>50</v>
@@ -980,7 +980,7 @@
         <v>613</v>
       </c>
       <c r="D19" s="9">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>53</v>
@@ -997,7 +997,7 @@
         <v>3432</v>
       </c>
       <c r="D20" s="9">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>56</v>
@@ -1014,7 +1014,7 @@
         <v>855</v>
       </c>
       <c r="D21" s="9">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>59</v>
@@ -1031,7 +1031,7 @@
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>14138</v>
+        <v>13768</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>

--- a/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
+++ b/data/Export_Monitoring_SLS_Kabupaten_Kota.xlsx
@@ -16,7 +16,7 @@
     <t>MONITORING SLS</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 3 Sep 2026, 12.04 | Dicetak: 3 Sep 2026, 13.25</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Sumber: FASIH Pendataan SE 2026 | Diperbarui: 5 Sep 2026, 06.04 | Dicetak: 5 Sep 2026, 06.50</t>
   </si>
   <si>
     <t>Kode</t>
@@ -55,7 +55,7 @@
     <t>LAMPUNG</t>
   </si>
   <si>
-    <t>27,88</t>
+    <t>28,53</t>
   </si>
   <si>
     <t>1801</t>
@@ -64,7 +64,7 @@
     <t>LAMPUNG BARAT</t>
   </si>
   <si>
-    <t>91</t>
+    <t>99,9</t>
   </si>
   <si>
     <t>1802</t>
@@ -73,7 +73,7 @@
     <t>TANGGAMUS</t>
   </si>
   <si>
-    <t>12,99</t>
+    <t>14,01</t>
   </si>
   <si>
     <t>1803</t>
@@ -82,7 +82,7 @@
     <t>LAMPUNG SELATAN</t>
   </si>
   <si>
-    <t>8,29</t>
+    <t>10,3</t>
   </si>
   <si>
     <t>1804</t>
@@ -91,7 +91,7 @@
     <t>LAMPUNG TIMUR</t>
   </si>
   <si>
-    <t>11,87</t>
+    <t>13,83</t>
   </si>
   <si>
     <t>1805</t>
@@ -100,7 +100,7 @@
     <t>LAMPUNG TENGAH</t>
   </si>
   <si>
-    <t>16,07</t>
+    <t>15,22</t>
   </si>
   <si>
     <t>1806</t>
@@ -109,7 +109,7 @@
     <t>LAMPUNG UTARA</t>
   </si>
   <si>
-    <t>79,07</t>
+    <t>78,92</t>
   </si>
   <si>
     <t>1807</t>
@@ -118,7 +118,7 @@
     <t>WAY KANAN</t>
   </si>
   <si>
-    <t>13,43</t>
+    <t>15,77</t>
   </si>
   <si>
     <t>1808</t>
@@ -127,7 +127,7 @@
     <t>TULANG BAWANG</t>
   </si>
   <si>
-    <t>26,62</t>
+    <t>29,21</t>
   </si>
   <si>
     <t>1809</t>
@@ -136,7 +136,7 @@
     <t>PESAWARAN</t>
   </si>
   <si>
-    <t>37,6</t>
+    <t>32,91</t>
   </si>
   <si>
     <t>1810</t>
@@ -145,7 +145,7 @@
     <t>PRINGSEWU</t>
   </si>
   <si>
-    <t>46,73</t>
+    <t>52,71</t>
   </si>
   <si>
     <t>1811</t>
@@ -154,7 +154,7 @@
     <t>MESUJI</t>
   </si>
   <si>
-    <t>41,34</t>
+    <t>35,46</t>
   </si>
   <si>
     <t>1812</t>
@@ -163,7 +163,7 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>89,86</t>
+    <t>87,44</t>
   </si>
   <si>
     <t>1813</t>
@@ -181,7 +181,7 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>4,37</t>
+    <t>5,91</t>
   </si>
   <si>
     <t>1872</t>
@@ -190,7 +190,7 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>15,91</t>
+    <t>17,19</t>
   </si>
   <si>
     <t/>
@@ -759,7 +759,7 @@
         <v>49386</v>
       </c>
       <c r="D6" s="6">
-        <v>13768</v>
+        <v>14092</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>14</v>
@@ -776,7 +776,7 @@
         <v>1011</v>
       </c>
       <c r="D7" s="9">
-        <v>920</v>
+        <v>1010</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>17</v>
@@ -793,7 +793,7 @@
         <v>2756</v>
       </c>
       <c r="D8" s="9">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>20</v>
@@ -810,7 +810,7 @@
         <v>5816</v>
       </c>
       <c r="D9" s="9">
-        <v>482</v>
+        <v>599</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>23</v>
@@ -827,7 +827,7 @@
         <v>6824</v>
       </c>
       <c r="D10" s="9">
-        <v>810</v>
+        <v>944</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>8607</v>
       </c>
       <c r="D11" s="9">
-        <v>1383</v>
+        <v>1310</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>29</v>
@@ -861,7 +861,7 @@
         <v>4022</v>
       </c>
       <c r="D12" s="9">
-        <v>3180</v>
+        <v>3174</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -878,7 +878,7 @@
         <v>2905</v>
       </c>
       <c r="D13" s="9">
-        <v>390</v>
+        <v>458</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>35</v>
@@ -895,7 +895,7 @@
         <v>3900</v>
       </c>
       <c r="D14" s="9">
-        <v>1038</v>
+        <v>1139</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>38</v>
@@ -912,7 +912,7 @@
         <v>2753</v>
       </c>
       <c r="D15" s="9">
-        <v>1035</v>
+        <v>906</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>41</v>
@@ -929,7 +929,7 @@
         <v>1605</v>
       </c>
       <c r="D16" s="9">
-        <v>750</v>
+        <v>846</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>44</v>
@@ -946,7 +946,7 @@
         <v>1802</v>
       </c>
       <c r="D17" s="9">
-        <v>745</v>
+        <v>639</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>47</v>
@@ -963,7 +963,7 @@
         <v>2485</v>
       </c>
       <c r="D18" s="9">
-        <v>2233</v>
+        <v>2173</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>50</v>
@@ -997,7 +997,7 @@
         <v>3432</v>
       </c>
       <c r="D20" s="9">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>56</v>
@@ -1014,7 +1014,7 @@
         <v>855</v>
       </c>
       <c r="D21" s="9">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>59</v>
@@ -1031,7 +1031,7 @@
         <v>49386</v>
       </c>
       <c r="D22" s="12">
-        <v>13768</v>
+        <v>14092</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>
